--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -1,92 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\Option 1\Test_automation_Option 1\Test_automation_Option 1\test_automation\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02121B89-E3DB-4032-8CF4-2C2976BCAEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19860" tabRatio="722" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
+    <sheet name=" Test cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Input length type</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Expected output</t>
-  </si>
-  <si>
-    <t>Actual output</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="8.5"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="8.5"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <color theme="1"/>
+      <sz val="8"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Iskoola Pota"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -133,46 +121,118 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -438,117 +498,3185 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M201"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="50" customHeight="1" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col width="10.83203125" customWidth="1" min="1" max="1"/>
+    <col width="22.1640625" customWidth="1" min="3" max="3"/>
+    <col width="25.33203125" customWidth="1" min="4" max="4"/>
+    <col width="22.5" customWidth="1" min="5" max="5"/>
+    <col width="14.33203125" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12.33203125" customWidth="1" min="9" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+    <row r="1" ht="36.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input length type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected output</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Actual output</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="50" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>oyta kohmadaaaa???</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>ඔයාට කොහොමද?</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>ඔයාට කොහොමද???</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0002</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>mamaaa yanawaaa 😅</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>මම යනවා 😅</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>මම යනවා</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0003</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>uumbataaa hodaidaaa 😅</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>උඹට හොඳයිද😅</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>උම්බට හොඳයිද 😅</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0004</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>api yannadaaa???</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>අපි යන්නද?</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>අපි යන්නද???</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0005</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>oyage nama mokakd??</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගේ නම මොකක්ද?</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගෙ නම මොකක්ද??</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="50" customHeight="1">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0006</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>ane mata help ekak dnn</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>අනේ මට help එකක් දෙන්න</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>අනේ මට help එකක් දාන්න</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="50" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="50" customHeight="1">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="50" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0007</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>mama ennnnnawa</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>මම එනවා</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>මම එන්නන්නවා</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="50" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="50" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="50" customHeight="1">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="50" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0008</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>oyata puluwanda brooo</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට පුළුවන්ද bro</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට පුලුවන්ද brooo</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="50" customHeight="1">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="50" customHeight="1">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="50" customHeight="1">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="50" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0009</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>mokakdaaaa mekaaaa 😡😡</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>මොකක්ද මේක</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>මොකක්ද මේකා?</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="50" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="50" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="50" customHeight="1">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="50" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0010</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>harrrrrriiiiii harrrriiiii 😅</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>හරි හරි</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>හරි හරි හරි හරි</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="50" customHeight="1">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="50" customHeight="1">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="50" customHeight="1">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="50" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0011</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>mamaaa ada office ekataaa yanawaaa buttt trafffic ekakkk 😅</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>මම අද office එකට යනවා but traffic එකක්</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>මම අද office එකට යනවා buttt traffic එකක් 😅</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="50" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="50" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="50" customHeight="1">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+    </row>
+    <row r="46" ht="50" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0012</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>oyala set eka hari fun ekak ne bn</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාලා set එක හරි fun එකක් නේ බන්</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාලා set එක හරි fun එකක් නෑ බං</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="50" customHeight="1">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="50" customHeight="1">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="50" customHeight="1">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="50" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0013</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>apiiii dennn on the wayyyy broooo wait karapannnn 😡</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>අපි දැන් on the way bro wait කරපන්</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>අපි දෙන්නා ඔන් තේ වය්ය්ය් broooo wait කරන්න 🤣</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="50" customHeight="1">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="50" customHeight="1">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="50" customHeight="1">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+    </row>
+    <row r="54" ht="50" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0014</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>mama call ekak denna try kala but na</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>මම call එකක් දෙන්න try කළා but නැ</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>මම call එකක් දෙන්න try කළා but නෑ</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="50" customHeight="1">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="50" customHeight="1">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+    </row>
+    <row r="58" ht="50" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0015</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>meeting eka 7.30pm wage patan gannawa</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>meeting එක 7.30pm වගේ පටන් ගන්නවා</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>meeting එක 7.30pm වගේ පටන් ගන්නවා</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="50" customHeight="1">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="50" customHeight="1">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="50" customHeight="1">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+    </row>
+    <row r="62" ht="50" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0016</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>mata Rs 2500k one bn urgent</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>මට Rs 2500ක් ඕන බන් urgent</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>මට Rs 2500ක් ඕනේ බන් urgent</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+    </row>
+    <row r="64" ht="50" customHeight="1">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+    </row>
+    <row r="65" ht="50" customHeight="1">
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+    </row>
+    <row r="66" ht="50" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0017</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>oyage wifi password eka mokadda bn</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගේ wifi password එක මොකක්ද බන්</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගෙ wifi password එක මොකද්ද බන්</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="50" customHeight="1">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+    </row>
+    <row r="68" ht="50" customHeight="1">
+      <c r="A68" s="5" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="5" t="n"/>
+    </row>
+    <row r="69" ht="50" customHeight="1">
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
+    </row>
+    <row r="70" ht="50" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0018</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>mama Zoom ekata join wenna try karanawa</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>මම Zoom එකට join වෙන්න try කරනවා</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>මම Zoom ඒකට ජොයින් වෙන්න try කරනවා</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="50" customHeight="1">
+      <c r="A71" s="5" t="n"/>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="5" t="n"/>
+    </row>
+    <row r="72" ht="50" customHeight="1">
+      <c r="A72" s="5" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+    </row>
+    <row r="73" ht="50" customHeight="1">
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n"/>
+    </row>
+    <row r="74" ht="50" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0019</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>teacher kiwwwwaaa asaaappp assignment ekaa dennaaa 😡</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>teacher කිව්වා asap assignment එක දෙන්න</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>teacher කිව්වාආආආආආආආආආආආප්ප assignment එක දෙන්නආආආආ</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="50" customHeight="1">
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="5" t="n"/>
+    </row>
+    <row r="76" ht="50" customHeight="1">
+      <c r="A76" s="5" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
+      <c r="F76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="50" customHeight="1">
+      <c r="A77" s="6" t="n"/>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="6" t="n"/>
+    </row>
+    <row r="78" ht="50" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0020</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>mata email ekak evanna puluwanda bn</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>මට email එකක් එවන්න පුළුවන්ද බන්</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>මට email එකක් එවන්න පුළුවන්ද බං</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="50" customHeight="1">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+    </row>
+    <row r="80" ht="50" customHeight="1">
+      <c r="A80" s="5" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+    </row>
+    <row r="81" ht="50" customHeight="1">
+      <c r="A81" s="6" t="n"/>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="6" t="n"/>
+    </row>
+    <row r="82" ht="50" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0021</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>apiiii Singaporeeee tripp ekakkk plannnn karanawaaa bn 😅</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>අපි Singapore trip එකක් plan කරනවා බන්</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>අපි Singapore එකක් plan කරන්න කරනවා බන් 😅</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="50" customHeight="1">
+      <c r="A83" s="5" t="n"/>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
+      <c r="F83" s="5" t="n"/>
+    </row>
+    <row r="84" ht="50" customHeight="1">
+      <c r="A84" s="5" t="n"/>
+      <c r="B84" s="5" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="5" t="n"/>
+    </row>
+    <row r="85" ht="50" customHeight="1">
+      <c r="A85" s="6" t="n"/>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="6" t="n"/>
+    </row>
+    <row r="86" ht="50" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0022</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>anura saha sunil dennama match eka gahuwa</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>අනුර සහ සුනිල් දෙන්නම match එක ගැහුවා</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>anura සහ සුනිල් දෙන්නම match එක ගැහුවා</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="50" customHeight="1">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+    </row>
+    <row r="88" ht="50" customHeight="1">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+    </row>
+    <row r="89" ht="50" customHeight="1">
+      <c r="A89" s="6" t="n"/>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="6" t="n"/>
+    </row>
+    <row r="90" ht="50" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0023</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>science paper ekata lamayi 100n 100 gaththa</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>science paper එකට ළමයි 100න් 100 ගත්ත</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>science paper එකට ළමයි 100න් 100 ගත්තා</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="50" customHeight="1">
+      <c r="A91" s="5" t="n"/>
+      <c r="B91" s="5" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+    </row>
+    <row r="92" ht="50" customHeight="1">
+      <c r="A92" s="5" t="n"/>
+      <c r="B92" s="5" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+    </row>
+    <row r="93" ht="50" customHeight="1">
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="6" t="n"/>
+    </row>
+    <row r="94" ht="50" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0024</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>meetinggg ekaaa 2026-02-06taaa schedulee karannaaaa 😡</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>meeting එක 2026-02-06ට schedule කරන්න</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>meetinggg එක 2026-0206ට චර්ගුලී කරන්න</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="50" customHeight="1">
+      <c r="A95" s="5" t="n"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="H95" s="2" t="n"/>
+      <c r="I95" s="2" t="n"/>
+      <c r="J95" s="2" t="n"/>
+      <c r="K95" s="2" t="n"/>
+    </row>
+    <row r="96" ht="50" customHeight="1">
+      <c r="A96" s="5" t="n"/>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+    </row>
+    <row r="97" ht="50" customHeight="1">
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="6" t="n"/>
+    </row>
+    <row r="98" ht="50" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0025</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>mamaaa km 3kkkk witharaa payinn giyaaa bn 😅</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>මම km 3ක් විතර පයින් ගියා බන්</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>මම km 3ක් විතර පයින් ගියා බන් 😅</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="50" customHeight="1">
+      <c r="A99" s="5" t="n"/>
+      <c r="B99" s="5" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="5" t="n"/>
+      <c r="F99" s="5" t="n"/>
+    </row>
+    <row r="100" ht="50" customHeight="1">
+      <c r="A100" s="5" t="n"/>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n"/>
+      <c r="F100" s="5" t="n"/>
+    </row>
+    <row r="101" ht="50" customHeight="1">
+      <c r="A101" s="6" t="n"/>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="n"/>
+    </row>
+    <row r="102" ht="50" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0026</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>uba mara kattak kala meka hari bn</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>උඹ මාර කට්ටක් කළා මේක හරි බන්</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>උඹ මාර කට්ටක් කාලා මේක හරි බන්</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
+    </row>
+    <row r="103" ht="50" customHeight="1">
+      <c r="A103" s="5" t="n"/>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
+      <c r="F103" s="5" t="n"/>
+      <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="n"/>
+    </row>
+    <row r="104" ht="50" customHeight="1">
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+    </row>
+    <row r="105" ht="50" customHeight="1">
+      <c r="A105" s="6" t="n"/>
+      <c r="B105" s="6" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="n"/>
+      <c r="E105" s="6" t="n"/>
+      <c r="F105" s="6" t="n"/>
+    </row>
+    <row r="106" ht="50" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0027</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>mee link eka balanna https://news.lk</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>මේ link එක බලන්න https://news.lk</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>මේ link එක බලන්න https://news.ල්ක්</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="50" customHeight="1">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="5" t="n"/>
+    </row>
+    <row r="108" ht="50" customHeight="1">
+      <c r="A108" s="5" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
+    </row>
+    <row r="109" ht="50" customHeight="1">
+      <c r="A109" s="6" t="n"/>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="6" t="n"/>
+    </row>
+    <row r="110" ht="50" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0028</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>email ekak evanna amal234@gmail.com</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>email එකක් එවන්න amal234@gmail.com</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>email එකක් එවන්න අමල්234@gmail.කොම්</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="50" customHeight="1">
+      <c r="A111" s="5" t="n"/>
+      <c r="B111" s="5" t="n"/>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="5" t="n"/>
+      <c r="F111" s="5" t="n"/>
+    </row>
+    <row r="112" ht="50" customHeight="1">
+      <c r="A112" s="5" t="n"/>
+      <c r="B112" s="5" t="n"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="5" t="n"/>
+    </row>
+    <row r="113" ht="50" customHeight="1">
+      <c r="A113" s="6" t="n"/>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="F113" s="6" t="n"/>
+    </row>
+    <row r="114" ht="50" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0029</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>@tharindu oyata message ekak damma bn</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>@tharindu ඔයාට message එකක් දැම්මා බන්</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>@තරිඳු ඔයාට message එකක් දැම්මා බන්</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="50" customHeight="1">
+      <c r="A115" s="5" t="n"/>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="5" t="n"/>
+      <c r="F115" s="5" t="n"/>
+    </row>
+    <row r="116" ht="50" customHeight="1">
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="5" t="n"/>
+      <c r="F116" s="5" t="n"/>
+    </row>
+    <row r="117" ht="50" customHeight="1">
+      <c r="A117" s="6" t="n"/>
+      <c r="B117" s="6" t="n"/>
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="n"/>
+      <c r="E117" s="6" t="n"/>
+      <c r="F117" s="6" t="n"/>
+    </row>
+    <row r="118" ht="50" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0030</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>mataaa denn pissuuu wageee hithennneee 😅😅😅😅</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>මට දැන් පිස්සු වගේ හිතෙන්නේ 😅😅</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>මට දෙන්න පිස්සු වගේ හිතෙන්නේ නැහැ 😅😅😅😅😅</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="50" customHeight="1">
+      <c r="A119" s="5" t="n"/>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="5" t="n"/>
+    </row>
+    <row r="120" ht="50" customHeight="1">
+      <c r="A120" s="5" t="n"/>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="5" t="n"/>
+      <c r="F120" s="5" t="n"/>
+    </row>
+    <row r="121" ht="50" customHeight="1">
+      <c r="A121" s="6" t="n"/>
+      <c r="B121" s="6" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+      <c r="E121" s="6" t="n"/>
+      <c r="F121" s="6" t="n"/>
+    </row>
+    <row r="122" ht="50" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0031</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>mama ada office ekata giya passe meeting ekak thibba but eka cancel una bn</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>මම අද office එකට ගියා පස්සේ meeting එකක් තිබ්බ but එක cancel උනා බන්</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>මම අද office එකට ගියා පස්සේ meeting එකක් තිබ්බා but එක cancel වුණා බන්</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="50" customHeight="1">
+      <c r="A123" s="5" t="n"/>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
+      <c r="E123" s="5" t="n"/>
+      <c r="F123" s="5" t="n"/>
+    </row>
+    <row r="124" ht="50" customHeight="1">
+      <c r="A124" s="5" t="n"/>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="5" t="n"/>
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="n"/>
+      <c r="K124" s="2" t="n"/>
+    </row>
+    <row r="125" ht="50" customHeight="1">
+      <c r="A125" s="6" t="n"/>
+      <c r="B125" s="6" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="6" t="n"/>
+      <c r="E125" s="6" t="n"/>
+      <c r="F125" s="6" t="n"/>
+    </row>
+    <row r="126" ht="50" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0032</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>api trip eka plan karanawapiiii tripp ekakkk plannnn karanawaaa nexttt monthtt Singaporeeee walataaa yannnaaa 😡a next month Singapore walata yanna hithan inne</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>අපි trip එක plan කරනවා next month Singapore වලට යන්න හිතන් ඉන්නේ</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>මම අද office එකට ගියා පස්සේ meeting එකක් තිබ්බා but එක cancel වුණා බන්</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="50" customHeight="1">
+      <c r="A127" s="5" t="n"/>
+      <c r="B127" s="5" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="5" t="n"/>
+    </row>
+    <row r="128" ht="50" customHeight="1">
+      <c r="A128" s="5" t="n"/>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n"/>
+      <c r="F128" s="5" t="n"/>
+    </row>
+    <row r="129" ht="50" customHeight="1">
+      <c r="A129" s="6" t="n"/>
+      <c r="B129" s="6" t="n"/>
+      <c r="C129" s="6" t="n"/>
+      <c r="D129" s="6" t="n"/>
+      <c r="E129" s="6" t="n"/>
+      <c r="F129" s="6" t="n"/>
+    </row>
+    <row r="130" ht="50" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0033</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>oyata puluwannam mage wede poddak balala feedback ekak denna bn</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට පුළුවන්නම් මගේ වැඩේ පොඩ්ඩක් බලලා feedback එකක් දෙන්න බන්</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>අපි trip එක plan කරනවාපැයි trip එකක් plan කරන්න කරනවාඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅඅ</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="50" customHeight="1">
+      <c r="A131" s="5" t="n"/>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="5" t="n"/>
+    </row>
+    <row r="132" ht="50" customHeight="1">
+      <c r="A132" s="5" t="n"/>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="5" t="n"/>
+      <c r="D132" s="5" t="n"/>
+      <c r="E132" s="5" t="n"/>
+      <c r="F132" s="5" t="n"/>
+    </row>
+    <row r="133" ht="50" customHeight="1">
+      <c r="A133" s="6" t="n"/>
+      <c r="B133" s="6" t="n"/>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="6" t="n"/>
+      <c r="E133" s="6" t="n"/>
+      <c r="F133" s="6" t="n"/>
+    </row>
+    <row r="134" ht="50" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0034</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>mama Zoom meeting ekata join wenna giya namuth connection eka hariyata na bn</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>මම Zoom meeting එකට join වෙන්න ගියා නමුත් connection එක හරියට නැ බන්</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට පුලුවන්නම් මගේ වැඩේ පොඩ්ඩක් බලලා feedback එකක් දෙන්න බන්</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="50" customHeight="1">
+      <c r="A135" s="5" t="n"/>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="5" t="n"/>
+    </row>
+    <row r="136" ht="50" customHeight="1">
+      <c r="A136" s="5" t="n"/>
+      <c r="B136" s="5" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="5" t="n"/>
+      <c r="F136" s="5" t="n"/>
+    </row>
+    <row r="137" ht="50" customHeight="1">
+      <c r="A137" s="6" t="n"/>
+      <c r="B137" s="6" t="n"/>
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="6" t="n"/>
+      <c r="E137" s="6" t="n"/>
+      <c r="F137" s="6" t="n"/>
+    </row>
+    <row r="138" ht="50" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0035</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>teacher kiwwa assignment eka email ekak widihata yawanna kiyala asap</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>teacher කිව්වා assignment එක email එකක් විදිහට යවන්න කියලා asap</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>මම Zoom meeting එකට join වෙන්න ගිය නමුත් connection එක හරියට නෑ බන්</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="50" customHeight="1">
+      <c r="A139" s="5" t="n"/>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
+      <c r="E139" s="5" t="n"/>
+      <c r="F139" s="5" t="n"/>
+    </row>
+    <row r="140" ht="50" customHeight="1">
+      <c r="A140" s="5" t="n"/>
+      <c r="B140" s="5" t="n"/>
+      <c r="C140" s="5" t="n"/>
+      <c r="D140" s="5" t="n"/>
+      <c r="E140" s="5" t="n"/>
+      <c r="F140" s="5" t="n"/>
+    </row>
+    <row r="141" ht="50" customHeight="1">
+      <c r="A141" s="6" t="n"/>
+      <c r="B141" s="6" t="n"/>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="6" t="n"/>
+      <c r="E141" s="6" t="n"/>
+      <c r="F141" s="6" t="n"/>
+    </row>
+    <row r="142" ht="50" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0036</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>mama kalin call karanna try kala namuth oyage phone eka off wela thibba</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>මම කලින් call කරන්න try කළා නමුත් ඔයාගේ phone එක off වෙලා තිබ්බ</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>teacher කිව්වා assignment එක email එකක් විදිහට යවන්න කියලා අසප්</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="50" customHeight="1">
+      <c r="A143" s="5" t="n"/>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="n"/>
+      <c r="E143" s="5" t="n"/>
+      <c r="F143" s="5" t="n"/>
+    </row>
+    <row r="144" ht="50" customHeight="1">
+      <c r="A144" s="5" t="n"/>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
+      <c r="E144" s="5" t="n"/>
+      <c r="F144" s="5" t="n"/>
+    </row>
+    <row r="145" ht="50" customHeight="1">
+      <c r="A145" s="6" t="n"/>
+      <c r="B145" s="6" t="n"/>
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+      <c r="E145" s="6" t="n"/>
+      <c r="F145" s="6" t="n"/>
+    </row>
+    <row r="146" ht="50" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0037</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>apiiii denn onnn theee wayyy wagee inneeee trafffic ekakkk nisaaa tikakkk lateeee 😅</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>අපි දැන් on the way වගේ ඉන්නේ traffic එකක් නිසා ටිකක් late වෙන්න පුළුවන්</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>මම කලින් call කරන්න try කළා නමුත් ඔයාගේ phone එක off වෙලා තිබ්බා</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="50" customHeight="1">
+      <c r="A147" s="5" t="n"/>
+      <c r="B147" s="5" t="n"/>
+      <c r="C147" s="5" t="n"/>
+      <c r="D147" s="5" t="n"/>
+      <c r="E147" s="5" t="n"/>
+      <c r="F147" s="5" t="n"/>
+    </row>
+    <row r="148" ht="50" customHeight="1">
+      <c r="A148" s="5" t="n"/>
+      <c r="B148" s="5" t="n"/>
+      <c r="C148" s="5" t="n"/>
+      <c r="D148" s="5" t="n"/>
+      <c r="E148" s="5" t="n"/>
+      <c r="F148" s="5" t="n"/>
+    </row>
+    <row r="149" ht="50" customHeight="1">
+      <c r="A149" s="6" t="n"/>
+      <c r="B149" s="6" t="n"/>
+      <c r="C149" s="6" t="n"/>
+      <c r="D149" s="6" t="n"/>
+      <c r="E149" s="6" t="n"/>
+      <c r="F149" s="6" t="n"/>
+    </row>
+    <row r="150" ht="50" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0038</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>mata hithenne me system eka hariyata wada karanne na bn bugs godak thiyenawa</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>මට හිතෙන්නේ මේ system එක හරියට වැඩ කරන්නේ නැ බන් bugs ගොඩක් තියෙනවා</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>අපි දෙන්න ඕන්න තේ වයි වගේ ඉන්නේ ට්රබ්ෆික් එකක් නිසා ටිකක් ලෑටී 😅</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="50" customHeight="1">
+      <c r="A151" s="5" t="n"/>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
+      <c r="E151" s="5" t="n"/>
+      <c r="F151" s="5" t="n"/>
+    </row>
+    <row r="152" ht="50" customHeight="1">
+      <c r="A152" s="5" t="n"/>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="5" t="n"/>
+      <c r="E152" s="5" t="n"/>
+      <c r="F152" s="5" t="n"/>
+    </row>
+    <row r="153" ht="50" customHeight="1">
+      <c r="A153" s="6" t="n"/>
+      <c r="B153" s="6" t="n"/>
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="6" t="n"/>
+      <c r="E153" s="6" t="n"/>
+      <c r="F153" s="6" t="n"/>
+    </row>
+    <row r="154" ht="50" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0039</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>oyage password eka change karanna puluwannam ekata strong ekak danna bn</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගේ password එක change කරන්න පුළුවන්නම් එකට strong එකක් දාන්න බන්</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>මට හිතෙන්නේ මේ system එක හරියට වැඩ කරන්නේ නෑ බන් bugs ගොඩක් තියෙනවා</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="50" customHeight="1">
+      <c r="A155" s="5" t="n"/>
+      <c r="B155" s="5" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+      <c r="E155" s="5" t="n"/>
+      <c r="F155" s="5" t="n"/>
+    </row>
+    <row r="156" ht="50" customHeight="1">
+      <c r="A156" s="5" t="n"/>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
+      <c r="E156" s="5" t="n"/>
+      <c r="F156" s="5" t="n"/>
+    </row>
+    <row r="157" ht="50" customHeight="1">
+      <c r="A157" s="6" t="n"/>
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+      <c r="E157" s="6" t="n"/>
+      <c r="F157" s="6" t="n"/>
+    </row>
+    <row r="158" ht="50" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0040</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>mama den balagena idala athi wela thiyenne 😡 meka hariyata wenas karanna one</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>මම දැන් බලගෙන ඉඳලා ඇති වෙලා තියෙන්නේ 😡 මේක හරියට වෙනස් කරන්න ඕන</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාගෙ password එක change කරන්න පුලුවන්නම් ඒකට strong එකක් දාන්න බන්</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="50" customHeight="1">
+      <c r="A159" s="5" t="n"/>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="5" t="n"/>
+      <c r="D159" s="5" t="n"/>
+      <c r="E159" s="5" t="n"/>
+      <c r="F159" s="5" t="n"/>
+    </row>
+    <row r="160" ht="50" customHeight="1">
+      <c r="A160" s="5" t="n"/>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="5" t="n"/>
+      <c r="F160" s="5" t="n"/>
+    </row>
+    <row r="161" ht="50" customHeight="1">
+      <c r="A161" s="6" t="n"/>
+      <c r="B161" s="6" t="n"/>
+      <c r="C161" s="6" t="n"/>
+      <c r="D161" s="6" t="n"/>
+      <c r="E161" s="6" t="n"/>
+      <c r="F161" s="6" t="n"/>
+    </row>
+    <row r="162" ht="50" customHeight="1">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0041</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>oyataaa hariyataaa therenawadaaaa 😡😡</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට හරියට තේරෙනවද</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>මම දැන් බලාගෙන ඉදලා ඇති වෙලා තියෙන්නේ 🤣 මෙක හරියට වෙනස් කරන්න ඕනේ</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="50" customHeight="1">
+      <c r="A163" s="5" t="n"/>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
+      <c r="E163" s="5" t="n"/>
+      <c r="F163" s="5" t="n"/>
+    </row>
+    <row r="164" ht="50" customHeight="1">
+      <c r="A164" s="5" t="n"/>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="n"/>
+      <c r="D164" s="5" t="n"/>
+      <c r="E164" s="5" t="n"/>
+      <c r="F164" s="5" t="n"/>
+    </row>
+    <row r="165" ht="50" customHeight="1">
+      <c r="A165" s="6" t="n"/>
+      <c r="B165" s="6" t="n"/>
+      <c r="C165" s="6" t="n"/>
+      <c r="D165" s="6" t="n"/>
+      <c r="E165" s="6" t="n"/>
+      <c r="F165" s="6" t="n"/>
+    </row>
+    <row r="166" ht="50" customHeight="1">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0042</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>mataaa pissuu hadenawaaaa bn 😅😅😅</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>මට පිස්සු හැදෙනවා බන් 😅</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට හරියට තේරෙනවද</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="50" customHeight="1">
+      <c r="A167" s="5" t="n"/>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
+      <c r="E167" s="5" t="n"/>
+      <c r="F167" s="5" t="n"/>
+    </row>
+    <row r="168" ht="50" customHeight="1">
+      <c r="A168" s="5" t="n"/>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="5" t="n"/>
+      <c r="D168" s="5" t="n"/>
+      <c r="E168" s="5" t="n"/>
+      <c r="F168" s="5" t="n"/>
+      <c r="J168" s="2" t="n"/>
+      <c r="K168" s="2" t="n"/>
+      <c r="L168" s="2" t="n"/>
+      <c r="M168" s="2" t="n"/>
+    </row>
+    <row r="169" ht="50" customHeight="1">
+      <c r="A169" s="6" t="n"/>
+      <c r="B169" s="6" t="n"/>
+      <c r="C169" s="6" t="n"/>
+      <c r="D169" s="6" t="n"/>
+      <c r="E169" s="6" t="n"/>
+      <c r="F169" s="6" t="n"/>
+    </row>
+    <row r="170" ht="50" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0043</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>umbata kiyannam eka hari bn</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>උඹට කියන්නම් එක හරි බන්</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>මට පිස්සු හැදෙනවා බන් 😅😅😅</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="50" customHeight="1">
+      <c r="A171" s="5" t="n"/>
+      <c r="B171" s="5" t="n"/>
+      <c r="C171" s="5" t="n"/>
+      <c r="D171" s="5" t="n"/>
+      <c r="E171" s="5" t="n"/>
+      <c r="F171" s="5" t="n"/>
+    </row>
+    <row r="172" ht="50" customHeight="1">
+      <c r="A172" s="5" t="n"/>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+      <c r="E172" s="5" t="n"/>
+      <c r="F172" s="5" t="n"/>
+    </row>
+    <row r="173" ht="50" customHeight="1">
+      <c r="A173" s="6" t="n"/>
+      <c r="B173" s="6" t="n"/>
+      <c r="C173" s="6" t="n"/>
+      <c r="D173" s="6" t="n"/>
+      <c r="E173" s="6" t="n"/>
+      <c r="F173" s="6" t="n"/>
+    </row>
+    <row r="174" ht="50" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0044</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>oyalalaaaa kohomadaaa inneeeee 😡</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාලා කොහොමද ඉන්නේ</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>උඹට කියන්නම් ඒක හරි බන්</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="50" customHeight="1">
+      <c r="A175" s="5" t="n"/>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="5" t="n"/>
+      <c r="D175" s="5" t="n"/>
+      <c r="E175" s="5" t="n"/>
+      <c r="F175" s="5" t="n"/>
+    </row>
+    <row r="176" ht="50" customHeight="1">
+      <c r="A176" s="5" t="n"/>
+      <c r="B176" s="5" t="n"/>
+      <c r="C176" s="5" t="n"/>
+      <c r="D176" s="5" t="n"/>
+      <c r="E176" s="5" t="n"/>
+      <c r="F176" s="5" t="n"/>
+    </row>
+    <row r="177" ht="50" customHeight="1">
+      <c r="A177" s="6" t="n"/>
+      <c r="B177" s="6" t="n"/>
+      <c r="C177" s="6" t="n"/>
+      <c r="D177" s="6" t="n"/>
+      <c r="E177" s="6" t="n"/>
+      <c r="F177" s="6" t="n"/>
+    </row>
+    <row r="178" ht="50" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0045</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>mokadda me seen eka bn</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>මොකක්ද මේ scene එක බන්</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාලලා කොහොමද ඉන්නේ</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="50" customHeight="1">
+      <c r="A179" s="5" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="5" t="n"/>
+      <c r="F179" s="5" t="n"/>
+    </row>
+    <row r="180" ht="50" customHeight="1">
+      <c r="A180" s="5" t="n"/>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
+      <c r="E180" s="5" t="n"/>
+      <c r="F180" s="5" t="n"/>
+    </row>
+    <row r="181" ht="50" customHeight="1">
+      <c r="A181" s="6" t="n"/>
+      <c r="B181" s="6" t="n"/>
+      <c r="C181" s="6" t="n"/>
+      <c r="D181" s="6" t="n"/>
+      <c r="E181" s="6" t="n"/>
+      <c r="F181" s="6" t="n"/>
+    </row>
+    <row r="182" ht="50" customHeight="1">
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0046</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>api set wenawada hetaaaa</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>අපි set වෙන්නවද හෙට</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>මොකද්ද මේ සීන් එක බන්</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="50" customHeight="1">
+      <c r="A183" s="5" t="n"/>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="5" t="n"/>
+      <c r="D183" s="5" t="n"/>
+      <c r="E183" s="5" t="n"/>
+      <c r="F183" s="5" t="n"/>
+    </row>
+    <row r="184" ht="50" customHeight="1">
+      <c r="A184" s="5" t="n"/>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="5" t="n"/>
+      <c r="D184" s="5" t="n"/>
+      <c r="E184" s="5" t="n"/>
+      <c r="F184" s="5" t="n"/>
+    </row>
+    <row r="185" ht="50" customHeight="1">
+      <c r="A185" s="6" t="n"/>
+      <c r="B185" s="6" t="n"/>
+      <c r="C185" s="6" t="n"/>
+      <c r="D185" s="6" t="n"/>
+      <c r="E185" s="6" t="n"/>
+      <c r="F185" s="6" t="n"/>
+    </row>
+    <row r="186" ht="50" customHeight="1">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0047</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>mama ennam tikak passeeee</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>මම එන්නම් ටිකක් පස්සේ</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>අපි set වෙනවද හෙට</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="50" customHeight="1">
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
+      <c r="E187" s="5" t="n"/>
+      <c r="F187" s="5" t="n"/>
+    </row>
+    <row r="188" ht="50" customHeight="1">
+      <c r="A188" s="5" t="n"/>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="5" t="n"/>
+      <c r="E188" s="5" t="n"/>
+      <c r="F188" s="5" t="n"/>
+    </row>
+    <row r="189" ht="50" customHeight="1">
+      <c r="A189" s="6" t="n"/>
+      <c r="B189" s="6" t="n"/>
+      <c r="C189" s="6" t="n"/>
+      <c r="D189" s="6" t="n"/>
+      <c r="E189" s="6" t="n"/>
+      <c r="F189" s="6" t="n"/>
+    </row>
+    <row r="190" ht="50" customHeight="1">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0048</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>oyataaa callll ekakkk dennaaa hadanawaaa bn 😅</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට call එකක් දෙන්න හදනවා බන්</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>මම එන්නම් ටිකක් පස්සෙඊ</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="50" customHeight="1">
+      <c r="A191" s="5" t="n"/>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="5" t="n"/>
+      <c r="E191" s="5" t="n"/>
+      <c r="F191" s="5" t="n"/>
+    </row>
+    <row r="192" ht="50" customHeight="1">
+      <c r="A192" s="5" t="n"/>
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
+      <c r="E192" s="5" t="n"/>
+      <c r="F192" s="5" t="n"/>
+    </row>
+    <row r="193" ht="50" customHeight="1">
+      <c r="A193" s="6" t="n"/>
+      <c r="B193" s="6" t="n"/>
+      <c r="C193" s="6" t="n"/>
+      <c r="D193" s="6" t="n"/>
+      <c r="E193" s="6" t="n"/>
+      <c r="F193" s="6" t="n"/>
+    </row>
+    <row r="194" ht="50" customHeight="1">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0049</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>mata help ekak one bn urgent</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>මට help එකක් ඕන බන් urgent</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>ඔයාට call එකක් දෙන්න හදනවා බන් 😅</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="50" customHeight="1">
+      <c r="A195" s="5" t="n"/>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
+      <c r="E195" s="5" t="n"/>
+      <c r="F195" s="5" t="n"/>
+    </row>
+    <row r="196" ht="50" customHeight="1">
+      <c r="A196" s="5" t="n"/>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="5" t="n"/>
+      <c r="F196" s="5" t="n"/>
+    </row>
+    <row r="197" ht="50" customHeight="1">
+      <c r="A197" s="6" t="n"/>
+      <c r="B197" s="6" t="n"/>
+      <c r="C197" s="6" t="n"/>
+      <c r="D197" s="6" t="n"/>
+      <c r="E197" s="6" t="n"/>
+      <c r="F197" s="6" t="n"/>
+    </row>
+    <row r="198" ht="50" customHeight="1">
+      <c r="A198" s="8" t="inlineStr">
+        <is>
+          <t>Neg_0050</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>hari bn mama balannammmm</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>හරි බන් මම බලන්නම්</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>මට help එකක් ඕනේ බන් urgent</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="50" customHeight="1">
+      <c r="A199" s="5" t="n"/>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="5" t="n"/>
+      <c r="D199" s="5" t="n"/>
+      <c r="E199" s="5" t="n"/>
+      <c r="F199" s="5" t="n"/>
+    </row>
+    <row r="200" ht="50" customHeight="1">
+      <c r="A200" s="5" t="n"/>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
+      <c r="E200" s="5" t="n"/>
+      <c r="F200" s="5" t="n"/>
+    </row>
+    <row r="201" ht="50" customHeight="1">
+      <c r="A201" s="6" t="n"/>
+      <c r="B201" s="6" t="n"/>
+      <c r="C201" s="6" t="n"/>
+      <c r="D201" s="6" t="n"/>
+      <c r="E201" s="6" t="n"/>
+      <c r="F201" s="6" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="300">
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="A166:A169"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="A162:A165"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="D198:D201"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="A146:A149"/>
+    <mergeCell ref="F198:F201"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="D174:D177"/>
+    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="A178:A181"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="D166:D169"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="E158:E161"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F94:F97"/>
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="B186:B189"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="E174:E177"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A150:A153"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="E130:E133"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="D178:D181"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="F178:F181"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="B170:B173"/>
+    <mergeCell ref="A174:A177"/>
+    <mergeCell ref="D170:D173"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="E186:E189"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="E170:E173"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="B174:B177"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="D182:D185"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="F182:F185"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="F166:F169"/>
+    <mergeCell ref="E198:E201"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="F162:F165"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E190:E193"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="F154:F157"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="A50:A53"/>
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="B162:B165"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="A186:A189"/>
+    <mergeCell ref="C186:C189"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="E142:E145"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="E194:E197"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="C170:C173"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="B190:B193"/>
     <mergeCell ref="D6:D9"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D190:D193"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="D86:D89"/>
     <mergeCell ref="F6:F9"/>
-    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="F142:F145"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="B182:B185"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="F134:F137"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="F194:F197"/>
+    <mergeCell ref="C198:C201"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="D162:D165"/>
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="C182:C185"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="E182:E185"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="A190:A193"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="F186:F189"/>
+    <mergeCell ref="C190:C193"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="C158:C161"/>
     <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
